--- a/FST16_Requirements.xlsx
+++ b/FST16_Requirements.xlsx
@@ -439,14 +439,14 @@
   <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
           <t>Aligned with the vehicle mass target (195 kg)</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -527,7 +527,7 @@
           <t>Physical Weighing of assembled corner</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01, 61816, 85X100X9 HMSA10 V</t>
         </is>
@@ -559,7 +559,7 @@
           <t>Matches peak DTI motor velocity at minimum planetary gear reduction ratio</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>CAD and Data Sheets</t>
         </is>
@@ -569,7 +569,7 @@
           <t>Meter o carro a rodar motores (cavaletes, pista, banco de potencia)</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>HB_01, 61816, 85X100X9 HMSA10 V, TD</t>
         </is>
@@ -601,7 +601,7 @@
           <t>Establishes the physical envelopes to design around the new motor</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -611,7 +611,7 @@
           <t>Assembly Test</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>UP_01, UP_03, UP_04</t>
         </is>
@@ -643,7 +643,7 @@
           <t>Ensures proper gear meshing, bearing alignment, and torque output</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -653,7 +653,7 @@
           <t>Assembly Test and Post-Test Inspection</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01, TD</t>
         </is>
@@ -685,7 +685,7 @@
           <t>Guarantees packaging clearance (min 5 mm by T 2.6.4)</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -695,7 +695,7 @@
           <t>Assembly test</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>HB_01, UP_01</t>
         </is>
@@ -727,7 +727,7 @@
           <t>Ensures rigid mounting and clearance for the brake system</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -737,7 +737,7 @@
           <t>Brake System Installation test</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01</t>
         </is>
@@ -769,7 +769,7 @@
           <t>To ensure maximum performance in dynamic events</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FEA</t>
         </is>
@@ -779,7 +779,7 @@
           <t>With the jig of local stiffness and an adapter on the hub, apply loads with car in vertical stance</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>UP_01, UpperSupport Version</t>
         </is>
@@ -811,7 +811,7 @@
           <t>Ensures rapid repairs</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Benchmarked with FST15 service</t>
         </is>
@@ -821,7 +821,7 @@
           <t>Timed Disassembly Test in the workshop</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01, HB_02, UpperSupport Version</t>
         </is>
@@ -853,7 +853,7 @@
           <t>Facilitates rapid lubrication maintenance</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Benchmarked with FST15 service</t>
         </is>
@@ -863,7 +863,7 @@
           <t>Timed Oil Change Test in the workshop</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>UP_01, UP_02</t>
         </is>
@@ -895,7 +895,7 @@
           <t>Enables static camber changes between runs in a dynamic event</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Benchmarked with FST15 service</t>
         </is>
@@ -905,7 +905,7 @@
           <t>Timed Wheel Change Test in the workshop</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>UpperSupport Version, UP_01</t>
         </is>
@@ -937,7 +937,7 @@
           <t>Enables rapid tire swaps</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Benchmarked with FST15 service</t>
         </is>
@@ -947,7 +947,7 @@
           <t>Timed Wheel Change Test</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01, 61816</t>
         </is>
@@ -979,7 +979,7 @@
           <t>Enables motor servicing</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Benchmarked with FST15 service</t>
         </is>
@@ -989,7 +989,7 @@
           <t>Motor change</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>UP_01, UP_03, UP_04</t>
         </is>
@@ -1021,7 +1021,7 @@
           <t>Defined through Pugsley Method: A = vg ; B = g ; C = s; D = min ; E = vs</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Analytical and FEA</t>
         </is>
@@ -1031,7 +1031,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>UP_01, UpperSupport Version, HB_01</t>
         </is>
@@ -1063,7 +1063,7 @@
           <t>Prevents mechanical interference, under all wheel possible positions</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -1073,7 +1073,7 @@
           <t>Full Articulation Test on car</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>UP_01, UpperSupport Version</t>
         </is>
@@ -1105,7 +1105,7 @@
           <t>Prevents internal gear-to-upright contact (team requirement is 2mm but 1.5 facilitates design)</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -1115,7 +1115,7 @@
           <t>Measure with half the drivetrain assembled</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01, TD</t>
         </is>
@@ -1147,7 +1147,7 @@
           <t>Prevents catastrophic failure before ending FST16 competitions</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Data Sheet and FEA</t>
         </is>
@@ -1157,7 +1157,7 @@
           <t>Ensaio a fadiga</t>
         </is>
       </c>
-      <c r="H17" s="1" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01, 61816, 85X100X9 HMSA10 V</t>
         </is>
@@ -1189,7 +1189,7 @@
           <t>Allows trackside setup tuning</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -1199,7 +1199,7 @@
           <t>Inclinometro</t>
         </is>
       </c>
-      <c r="H18" s="1" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>UpperSupport Version, UP_01</t>
         </is>
@@ -1231,7 +1231,7 @@
           <t>Keeps structural natural frequency safely above drivetrain rotational parts frequency</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>FEA</t>
         </is>
@@ -1241,7 +1241,7 @@
           <t>Mesa de vibracao (apenas drivetrain ou carro todo)</t>
         </is>
       </c>
-      <c r="H19" s="1" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>HB_01, 61816, TD</t>
         </is>
@@ -1273,7 +1273,7 @@
           <t>Keeps bearings, rotary seals, O-rings and gear oil within rated thermal windows</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Data Sheet</t>
         </is>
@@ -1283,7 +1283,7 @@
           <t>Heating components individually or all components assembled in temperature controlled oven</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>61816, 85X100X9 HMSA10 V, UP_01</t>
         </is>
@@ -1315,7 +1315,7 @@
           <t>Prevents kinematic deviation from nominal values</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Technical Drawing</t>
         </is>
@@ -1325,7 +1325,7 @@
           <t>Scan of the Upright, and confirm real xyz positions</t>
         </is>
       </c>
-      <c r="H21" s="1" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>UP_01, UpperSupport Version</t>
         </is>
@@ -1357,7 +1357,7 @@
           <t>Prevents wheel assembly rotational eccentricity and imbalance due to mounting method play</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Technical Drawing</t>
         </is>
@@ -1367,7 +1367,7 @@
           <t>Measure wheel eccentricity and radial runout while rotating the wheel assembly</t>
         </is>
       </c>
-      <c r="H22" s="1" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>HB_01, 61816</t>
         </is>
@@ -1399,7 +1399,7 @@
           <t>To ensure maximum performance in dynamic events</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>FEA</t>
         </is>
@@ -1409,7 +1409,7 @@
           <t>With the jig of local stiffness and adapter on the hub, apply loads with car in vertical stance</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01</t>
         </is>
@@ -1441,7 +1441,7 @@
           <t>Minimizes possible problem with impossible geometries for the tools of the sponsors</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Speak directly to Sponsor</t>
         </is>
@@ -1451,7 +1451,7 @@
           <t>Upon receiving, perform a full inspection of the part geometry</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01</t>
         </is>
@@ -1483,7 +1483,7 @@
           <t>Minimizes possible problem with tolerances for the tools of the sponsors</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Speak directly to Sponsor</t>
         </is>
@@ -1493,7 +1493,7 @@
           <t>Upon receiving, verify all critical tolerances using precision equipment</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01</t>
         </is>
@@ -1525,7 +1525,7 @@
           <t>Mandatory technical inspection visibility</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>CAD / Visual Inspection</t>
         </is>
@@ -1535,7 +1535,7 @@
           <t>Scrutineering check</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>UP_01, UpperSupport Version</t>
         </is>
@@ -1567,7 +1567,7 @@
           <t>Solid steel or titanium fasteners required</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Calculations and Data Sheet</t>
         </is>
@@ -1577,7 +1577,7 @@
           <t>Technical inspection</t>
         </is>
       </c>
-      <c r="H27" s="1" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
@@ -1609,7 +1609,7 @@
           <t>Clearance from rim barrel across all articulation positions</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -1619,7 +1619,7 @@
           <t>Physical clearance gauge check</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>UP_01, HB_01</t>
         </is>
@@ -1651,7 +1651,7 @@
           <t>Enables paddock transport with shut off vehicle</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>CAD and Mechanical Architecture</t>
         </is>
@@ -1661,7 +1661,7 @@
           <t>Vehicle push test</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>HB_01, 61816</t>
         </is>
@@ -1693,7 +1693,7 @@
           <t>Fluid containment safety rule</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>CAD and Seal Selection</t>
         </is>
@@ -1703,7 +1703,7 @@
           <t>Tilt and pressure test</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>85X100X9 HMSA10 V, UP_03, UP_04</t>
         </is>
@@ -1735,7 +1735,7 @@
           <t>Thermal rating certification</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Data Sheet</t>
         </is>
@@ -1745,7 +1745,7 @@
           <t>Thermal test in oven</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>85X100X9 HMSA10 V, UP_03, UP_04</t>
         </is>
@@ -1777,7 +1777,7 @@
           <t>Ground protection envelope rule</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -1787,7 +1787,7 @@
           <t>Scrutineering ground plane check</t>
         </is>
       </c>
-      <c r="H32" s="1" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
@@ -1819,7 +1819,7 @@
           <t>Debris scatter containment</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>CAD and Material Certs</t>
         </is>
@@ -1829,7 +1829,7 @@
           <t>Scrutineering inspection</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
@@ -1861,7 +1861,7 @@
           <t>Critical fastener classification</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Fastener Schedule</t>
         </is>
@@ -1871,7 +1871,7 @@
           <t>BOM inspection</t>
         </is>
       </c>
-      <c r="H34" s="1" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>HB_02, UpperSupport Version, UP_01</t>
         </is>
@@ -1903,7 +1903,7 @@
           <t>Minimum bolt grade and metric sizing</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>BOM and Technical Drawings</t>
         </is>
@@ -1913,7 +1913,7 @@
           <t>Head stamping inspection</t>
         </is>
       </c>
-      <c r="H35" s="1" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>HB_02, UpperSupport Version, UP_01</t>
         </is>
@@ -1945,7 +1945,7 @@
           <t>Standard bolt geometry types</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>BOM and Technical Drawings</t>
         </is>
@@ -1955,7 +1955,7 @@
           <t>Visual verification</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>HB_02, UpperSupport Version, UP_01</t>
         </is>
@@ -1987,7 +1987,7 @@
           <t>Fastener equivalency justification path</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>SES / Equivalency Calculations</t>
         </is>
@@ -1997,7 +1997,7 @@
           <t>Scrutineering approval</t>
         </is>
       </c>
-      <c r="H37" s="1" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>UpperSupport Version, UP_01</t>
         </is>
@@ -2029,7 +2029,7 @@
           <t>Mandatory positive locking for all critical fasteners</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Technical Drawings</t>
         </is>
@@ -2039,7 +2039,7 @@
           <t>Scrutineering inspection</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>HB_02, UpperSupport Version, UP_01</t>
         </is>
@@ -2071,7 +2071,7 @@
           <t>Compliant positive locking mechanisms definition</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Assembly Drawings</t>
         </is>
@@ -2081,7 +2081,7 @@
           <t>Scrutineering inspection</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>HB_02, UpperSupport Version, UP_01</t>
         </is>
@@ -2113,7 +2113,7 @@
           <t>Thread engagement requirement</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>CAD and Bolt Sizing</t>
         </is>
@@ -2123,7 +2123,7 @@
           <t>Physical thread protrusion check</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>HB_02, UpperSupport Version, UP_01</t>
         </is>
@@ -2155,7 +2155,7 @@
           <t>Spherical joint pop-out prevention</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -2165,7 +2165,7 @@
           <t>Safety washer diameter check</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>UpperSupport Version, UP_01</t>
         </is>
@@ -2197,7 +2197,7 @@
           <t>Toe link locking requirement</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
@@ -2207,7 +2207,7 @@
           <t>Physical inspection</t>
         </is>
       </c>
-      <c r="H42" s="1" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
@@ -2239,7 +2239,7 @@
           <t>Does not constrain current design: FST16 uses 4/6-bolt pattern hub rather than single center-lock retaining nut.</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Concept Review</t>
         </is>
@@ -2249,7 +2249,7 @@
           <t>Concept validation</t>
         </is>
       </c>
-      <c r="H43" s="1" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
@@ -2281,7 +2281,7 @@
           <t>Does not constrain current design: Steel fasteners selected for wheel attachment.</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Concept Review</t>
         </is>
@@ -2291,7 +2291,7 @@
           <t>Concept validation</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>HB_01</t>
         </is>
@@ -2323,7 +2323,7 @@
           <t>Does not constrain current design: Planetary gearbox is fully enclosed within the sealed upright housing; no exposed chains/belts/gears.</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>CAD Architecture</t>
         </is>
@@ -2333,7 +2333,7 @@
           <t>Concept validation</t>
         </is>
       </c>
-      <c r="H45" s="1" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>UP_01</t>
         </is>
@@ -2365,7 +2365,7 @@
           <t>Does not constrain current design: In-hub motor is contained within the structural upright and wheel rim assembly.</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Packaging CAD</t>
         </is>
@@ -2375,7 +2375,7 @@
           <t>Concept validation</t>
         </is>
       </c>
-      <c r="H46" s="1" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>UP_01, UP_03, UP_04</t>
         </is>

--- a/FST16_Requirements.xlsx
+++ b/FST16_Requirements.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>UP_01, UpperSupport Version</t>
+          <t>UP_01, HB_01, UpperSupport Version</t>
         </is>
       </c>
     </row>
